--- a/SeleniumTests/TestDataFolder/LoginTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/LoginTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B015CC-74B4-4CB8-BB77-97C8579B1DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5E11D16-6A5E-4E92-9CD4-130787B7BDC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ForgotPasswordTestData" sheetId="1" r:id="rId1"/>
@@ -27,10 +27,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>email</t>
+    <t>yanshen.choo@qubeapps.com</t>
   </si>
   <si>
-    <t>yanshen.choo@qubeapps.com</t>
+    <t>Email</t>
   </si>
 </sst>
 </file>
@@ -361,15 +361,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
